--- a/output/pdf_financials_xlsx/BARU.xlsx
+++ b/output/pdf_financials_xlsx/BARU.xlsx
@@ -6041,52 +6041,52 @@
         <v>2.342023</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>14.977315</v>
+        <v>15.319933</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>17.185638</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>18.13793</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>18.500385</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>18.553917</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>18.553917</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>18.553917</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>19.091514</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>19.301689</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>19.325152</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>19.451055</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>21.686422</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>22.248753</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>22.314375</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>22.377049</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>23.25629</v>
       </c>
     </row>
     <row r="93">
@@ -10397,7 +10397,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11666,7 +11670,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -13105,7 +13113,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13915,7 +13927,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -14307,7 +14323,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BARU.xlsx
+++ b/output/pdf_financials_xlsx/BARU.xlsx
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.070255</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.066423</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00859</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-10.333173</v>
+        <v>-10.403428</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-9.342371999999999</v>
+        <v>-9.408795</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-24.485629</v>
+        <v>-24.494219</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-12.291801</v>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-10.283589</v>
+        <v>-10.353844</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-9.257668000000001</v>
+        <v>-9.324090999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-24.408115</v>
+        <v>-24.416705</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-12.269363</v>
@@ -7996,22 +7996,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.030939</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.030654</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.138325</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.118745</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027273</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.10786</v>
       </c>
     </row>
     <row r="125">
@@ -8058,22 +8058,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.030939</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.030654</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.138325</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.118745</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027273</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.10786</v>
       </c>
     </row>
     <row r="126">
@@ -18070,7 +18070,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -25343,7 +25347,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -42315,7 +42319,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -44745,7 +44749,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -47900,7 +47904,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
